--- a/virtual_event_forms/038_zoom_appointment_form--virtual_event_forms.xlsx
+++ b/virtual_event_forms/038_zoom_appointment_form--virtual_event_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -822,12 +822,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'zoom'}</t>
+          <t>zoom</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Zoom'}</t>
+          <t>Zoom</t>
         </is>
       </c>
     </row>
@@ -872,80 +872,80 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'zoom'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Zoom'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>provider_info_choices</t>
+          <t>participant_info_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>participant_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Participant 1</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>provider_info_choices</t>
+          <t>participant_info_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>participant_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Participant 2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>participant_info_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'participant_1'}</t>
+          <t>pay_now</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Participant 1'}</t>
+          <t>Pay Now</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>participant_info_choices</t>
+          <t>payment_method_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'participant_2'}</t>
+          <t>pay_later</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Participant 2'}</t>
+          <t>Pay Later</t>
         </is>
       </c>
     </row>
@@ -957,63 +957,63 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'pay_now'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Pay Now'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_status_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'pay_later'}</t>
+          <t>paid</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Pay Later'}</t>
+          <t>Paid</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_status_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>unpaid</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Unpaid</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>payment_method_choices</t>
+          <t>payment_status_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'other'}</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Other'}</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -1025,182 +1025,114 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'paid'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Paid'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>payment_status_choices</t>
+          <t>participant_role_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'unpaid'}</t>
+          <t>host</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Unpaid'}</t>
+          <t>Host</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>payment_status_choices</t>
+          <t>participant_role_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'pending'}</t>
+          <t>participant</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Pending'}</t>
+          <t>Participant</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>payment_status_choices</t>
+          <t>appointment_status_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'cancelled'}</t>
+          <t>scheduled</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Cancelled'}</t>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>participant_role_choices</t>
+          <t>appointment_status_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'host'}</t>
+          <t>unavailable</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Host'}</t>
+          <t>Unavailable</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>participant_role_choices</t>
+          <t>appointment_status_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'host'}</t>
+          <t>available</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Host'}</t>
+          <t>Available</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>participant_role_choices</t>
+          <t>appointment_status_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'participant'}</t>
+          <t>cancelled</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'Participant'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>appointment_status_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>{'value':_'scheduled'}</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>{'value': 'Scheduled'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>appointment_status_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>{'value':_'unavailable'}</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>{'value': 'Unavailable'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>appointment_status_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>{'value':_'available'}</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>{'value': 'Available'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>appointment_status_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>{'value':_'cancelled'}</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>{'value': 'Cancelled'}</t>
+          <t>Cancelled</t>
         </is>
       </c>
     </row>
